--- a/Sales Data.xlsx
+++ b/Sales Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Excel\Excel_Project_Work\Project 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24BF0B54-A3C5-497B-A38A-83B8851256AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345891A9-AB4E-420B-83C8-35D1049473FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7A03000F-CE6F-434D-94EB-643CC0F60A3A}"/>
   </bookViews>
@@ -1107,15 +1107,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1167,17 +1158,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="double">
         <color theme="0"/>
@@ -1201,12 +1181,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color theme="0"/>
+      </top>
+      <bottom style="double">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1424,19 +1426,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1469,13 +1459,34 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1521,12 +1532,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3394,49 +3399,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3521,49 +3484,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3648,49 +3569,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent3">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent3">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3775,49 +3654,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent4">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent4">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent4">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3902,49 +3739,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent5">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent5">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent5">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4920,8 +4715,7 @@
           <a:sp3d prstMaterial="matte"/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4991,7 +4785,7 @@
         <c:idx val="9"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5014,7 +4808,7 @@
         <c:idx val="10"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5037,7 +4831,7 @@
         <c:idx val="11"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent4"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5060,7 +4854,7 @@
         <c:idx val="12"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent5"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -5713,7 +5507,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -12702,8 +12495,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>903392</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="33" name="Region">
@@ -12726,7 +12519,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12736,8 +12529,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="51646" y="4511674"/>
-              <a:ext cx="1813560" cy="2276051"/>
+              <a:off x="51646" y="4366745"/>
+              <a:ext cx="1813560" cy="2220271"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -12856,8 +12649,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>347134</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="15" name="Months (Order_Date)">
@@ -12880,7 +12673,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -12890,8 +12683,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1938866" y="2472268"/>
-              <a:ext cx="1712807" cy="3759199"/>
+              <a:off x="1938866" y="2404036"/>
+              <a:ext cx="1712807" cy="3626722"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -12948,7 +12741,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="105624" y="70862"/>
-          <a:ext cx="14001927" cy="487435"/>
+          <a:ext cx="15535064" cy="487435"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12959,23 +12752,30 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="accent1">
-                <a:lumMod val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="48000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="97000"/>
-                <a:lumOff val="3000"/>
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="60000"/>
-                <a:lumOff val="40000"/>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx2">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx2">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="1"/>
           <a:tileRect/>
         </a:gradFill>
         <a:ln>
@@ -13100,8 +12900,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>973666</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" Requires="tsle">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
+      <mc:Choice Requires="tsle">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Order_Date">
@@ -13119,12 +12919,12 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2012/timeslicer">
-              <tsle:timeslicer xmlns:tsle="http://schemas.microsoft.com/office/drawing/2012/timeslicer" name="Order_Date"/>
+              <tsle:timeslicer name="Order_Date"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13134,8 +12934,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3815927" y="5638800"/>
-              <a:ext cx="5548205" cy="1219199"/>
+              <a:off x="3819912" y="5452035"/>
+              <a:ext cx="5548205" cy="1205255"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -19920,390 +19720,397 @@
     <col min="24" max="16384" width="8.88671875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="50.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="89"/>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="89"/>
-      <c r="S1" s="89"/>
-      <c r="T1" s="89"/>
-      <c r="U1" s="89"/>
-      <c r="V1" s="89"/>
-      <c r="W1" s="90"/>
+    <row r="1" spans="1:24" ht="50.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="105"/>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="106"/>
+      <c r="M1" s="106"/>
+      <c r="N1" s="106"/>
+      <c r="O1" s="106"/>
+      <c r="P1" s="106"/>
+      <c r="Q1" s="106"/>
+      <c r="R1" s="106"/>
+      <c r="S1" s="106"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="106"/>
+      <c r="V1" s="106"/>
+      <c r="W1" s="107"/>
       <c r="X1" s="63"/>
     </row>
     <row r="2" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="103"/>
       <c r="O2" s="62"/>
-      <c r="W2" s="87"/>
+      <c r="W2" s="86"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="W3" s="87"/>
+      <c r="A3" s="103"/>
+      <c r="W3" s="86"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="W4" s="87"/>
+      <c r="A4" s="103"/>
+      <c r="W4" s="86"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="W5" s="87"/>
+      <c r="A5" s="103"/>
+      <c r="W5" s="86"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="W6" s="87"/>
+      <c r="A6" s="103"/>
+      <c r="W6" s="86"/>
     </row>
     <row r="7" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="85"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="85"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
-      <c r="L7" s="85"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="85"/>
-      <c r="O7" s="85"/>
-      <c r="P7" s="85"/>
-      <c r="Q7" s="85"/>
-      <c r="R7" s="85"/>
-      <c r="S7" s="85"/>
-      <c r="T7" s="85"/>
-      <c r="U7" s="85"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="88"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="84"/>
+      <c r="O7" s="84"/>
+      <c r="P7" s="84"/>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="84"/>
+      <c r="S7" s="84"/>
+      <c r="T7" s="84"/>
+      <c r="U7" s="84"/>
+      <c r="V7" s="84"/>
+      <c r="W7" s="87"/>
     </row>
     <row r="8" spans="1:24" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="86"/>
-      <c r="L8" s="86"/>
-      <c r="W8" s="87"/>
+      <c r="A8" s="103"/>
+      <c r="C8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="W8" s="86"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="84"/>
-      <c r="C9" s="87"/>
-      <c r="L9" s="87"/>
-      <c r="W9" s="87"/>
+      <c r="A9" s="103"/>
+      <c r="C9" s="86"/>
+      <c r="L9" s="86"/>
+      <c r="W9" s="86"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="84"/>
-      <c r="C10" s="87"/>
-      <c r="L10" s="87"/>
-      <c r="W10" s="87"/>
+      <c r="A10" s="103"/>
+      <c r="C10" s="86"/>
+      <c r="L10" s="86"/>
+      <c r="W10" s="86"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="84"/>
-      <c r="C11" s="87"/>
-      <c r="L11" s="87"/>
-      <c r="W11" s="87"/>
+      <c r="A11" s="103"/>
+      <c r="C11" s="86"/>
+      <c r="L11" s="86"/>
+      <c r="W11" s="86"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
-      <c r="C12" s="87"/>
-      <c r="L12" s="87"/>
-      <c r="W12" s="87"/>
+      <c r="A12" s="103"/>
+      <c r="C12" s="86"/>
+      <c r="L12" s="86"/>
+      <c r="W12" s="86"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="84"/>
-      <c r="C13" s="87"/>
-      <c r="L13" s="87"/>
-      <c r="W13" s="87"/>
+      <c r="A13" s="103"/>
+      <c r="C13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="W13" s="86"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="84"/>
-      <c r="C14" s="87"/>
-      <c r="L14" s="87"/>
-      <c r="W14" s="87"/>
+      <c r="A14" s="103"/>
+      <c r="C14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="W14" s="86"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="84"/>
-      <c r="C15" s="87"/>
-      <c r="L15" s="87"/>
-      <c r="W15" s="87"/>
+      <c r="A15" s="103"/>
+      <c r="C15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="W15" s="86"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="84"/>
-      <c r="C16" s="87"/>
-      <c r="L16" s="87"/>
-      <c r="W16" s="87"/>
+      <c r="A16" s="103"/>
+      <c r="C16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="W16" s="86"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="84"/>
-      <c r="C17" s="87"/>
-      <c r="L17" s="87"/>
-      <c r="W17" s="87"/>
+      <c r="A17" s="103"/>
+      <c r="C17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="W17" s="86"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="84"/>
-      <c r="C18" s="87"/>
-      <c r="L18" s="87"/>
-      <c r="W18" s="87"/>
+      <c r="A18" s="103"/>
+      <c r="C18" s="86"/>
+      <c r="L18" s="86"/>
+      <c r="W18" s="86"/>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="84"/>
-      <c r="C19" s="87"/>
-      <c r="L19" s="87"/>
-      <c r="W19" s="87"/>
+      <c r="A19" s="103"/>
+      <c r="C19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="W19" s="86"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" s="84"/>
-      <c r="C20" s="87"/>
-      <c r="L20" s="87"/>
-      <c r="W20" s="87"/>
+      <c r="A20" s="103"/>
+      <c r="C20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="W20" s="86"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="84"/>
-      <c r="C21" s="87"/>
-      <c r="L21" s="87"/>
-      <c r="W21" s="87"/>
+      <c r="A21" s="103"/>
+      <c r="C21" s="86"/>
+      <c r="L21" s="86"/>
+      <c r="W21" s="86"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="84"/>
-      <c r="C22" s="87"/>
-      <c r="L22" s="87"/>
-      <c r="W22" s="87"/>
+      <c r="A22" s="103"/>
+      <c r="C22" s="86"/>
+      <c r="L22" s="86"/>
+      <c r="W22" s="86"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="84"/>
-      <c r="C23" s="87"/>
-      <c r="L23" s="87"/>
-      <c r="W23" s="87"/>
+      <c r="A23" s="103"/>
+      <c r="C23" s="86"/>
+      <c r="L23" s="86"/>
+      <c r="W23" s="86"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24" s="84"/>
-      <c r="C24" s="87"/>
-      <c r="L24" s="87"/>
-      <c r="W24" s="87"/>
+      <c r="A24" s="103"/>
+      <c r="C24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="W24" s="86"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25" s="84"/>
-      <c r="C25" s="87"/>
-      <c r="L25" s="87"/>
-      <c r="W25" s="87"/>
+      <c r="A25" s="103"/>
+      <c r="C25" s="86"/>
+      <c r="L25" s="86"/>
+      <c r="W25" s="86"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A26" s="84"/>
-      <c r="C26" s="87"/>
-      <c r="L26" s="87"/>
-      <c r="W26" s="87"/>
+      <c r="A26" s="103"/>
+      <c r="C26" s="86"/>
+      <c r="L26" s="86"/>
+      <c r="W26" s="86"/>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A27" s="84"/>
-      <c r="C27" s="87"/>
-      <c r="L27" s="87"/>
-      <c r="W27" s="87"/>
+      <c r="A27" s="103"/>
+      <c r="C27" s="86"/>
+      <c r="L27" s="86"/>
+      <c r="W27" s="86"/>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" s="84"/>
-      <c r="C28" s="87"/>
-      <c r="L28" s="87"/>
-      <c r="W28" s="87"/>
+      <c r="A28" s="103"/>
+      <c r="C28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="W28" s="86"/>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" s="84"/>
-      <c r="C29" s="87"/>
-      <c r="L29" s="87"/>
-      <c r="W29" s="87"/>
+      <c r="A29" s="103"/>
+      <c r="C29" s="86"/>
+      <c r="L29" s="86"/>
+      <c r="W29" s="86"/>
     </row>
     <row r="30" spans="1:23" ht="83.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="93"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="91"/>
-      <c r="E30" s="85"/>
-      <c r="F30" s="85"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="85"/>
-      <c r="I30" s="85"/>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="85"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="85"/>
-      <c r="P30" s="85"/>
-      <c r="Q30" s="85"/>
-      <c r="R30" s="85"/>
-      <c r="S30" s="85"/>
-      <c r="T30" s="85"/>
-      <c r="U30" s="85"/>
-      <c r="V30" s="85"/>
-      <c r="W30" s="88"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="88"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="84"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="87"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="84"/>
+      <c r="P30" s="84"/>
+      <c r="Q30" s="84"/>
+      <c r="R30" s="84"/>
+      <c r="S30" s="84"/>
+      <c r="T30" s="84"/>
+      <c r="U30" s="84"/>
+      <c r="V30" s="84"/>
+      <c r="W30" s="87"/>
     </row>
     <row r="31" spans="1:23" ht="35.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="124" t="s">
+      <c r="A31" s="108" t="s">
         <v>159</v>
       </c>
-      <c r="B31" s="124"/>
-      <c r="C31" s="125"/>
-      <c r="L31" s="87"/>
-      <c r="W31" s="87"/>
+      <c r="B31" s="108"/>
+      <c r="C31" s="109"/>
+      <c r="L31" s="86"/>
+      <c r="W31" s="86"/>
     </row>
     <row r="32" spans="1:23" ht="4.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="105"/>
-      <c r="B32" s="105"/>
-      <c r="C32" s="106"/>
-      <c r="L32" s="87"/>
-      <c r="W32" s="87"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="101"/>
+      <c r="C32" s="102"/>
+      <c r="L32" s="86"/>
+      <c r="W32" s="86"/>
     </row>
     <row r="33" spans="1:23" ht="4.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="105"/>
-      <c r="B33" s="105"/>
-      <c r="C33" s="106"/>
-      <c r="L33" s="87"/>
-      <c r="W33" s="87"/>
+      <c r="A33" s="104"/>
+      <c r="B33" s="101"/>
+      <c r="C33" s="102"/>
+      <c r="L33" s="86"/>
+      <c r="W33" s="86"/>
     </row>
     <row r="34" spans="1:23" ht="10.199999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="105"/>
-      <c r="B34" s="105"/>
-      <c r="C34" s="106"/>
-      <c r="L34" s="87"/>
-      <c r="W34" s="87"/>
+      <c r="A34" s="104"/>
+      <c r="B34" s="101"/>
+      <c r="C34" s="102"/>
+      <c r="L34" s="86"/>
+      <c r="W34" s="86"/>
     </row>
     <row r="35" spans="1:23" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="107" t="s">
+      <c r="A35" s="110" t="s">
         <v>161</v>
       </c>
-      <c r="B35" s="107"/>
-      <c r="C35" s="108"/>
-      <c r="L35" s="87"/>
-      <c r="W35" s="87"/>
+      <c r="B35" s="110"/>
+      <c r="C35" s="111"/>
+      <c r="L35" s="86"/>
+      <c r="W35" s="86"/>
     </row>
     <row r="36" spans="1:23" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="107"/>
-      <c r="B36" s="107"/>
-      <c r="C36" s="108"/>
-      <c r="L36" s="87"/>
-      <c r="W36" s="87"/>
+      <c r="A36" s="110"/>
+      <c r="B36" s="110"/>
+      <c r="C36" s="111"/>
+      <c r="L36" s="86"/>
+      <c r="W36" s="86"/>
     </row>
     <row r="37" spans="1:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="107" t="s">
+      <c r="A37" s="110" t="s">
         <v>162</v>
       </c>
-      <c r="B37" s="107"/>
-      <c r="C37" s="108"/>
-      <c r="L37" s="87"/>
-      <c r="W37" s="87"/>
+      <c r="B37" s="110"/>
+      <c r="C37" s="111"/>
+      <c r="L37" s="86"/>
+      <c r="W37" s="86"/>
     </row>
     <row r="38" spans="1:23" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="107"/>
-      <c r="B38" s="107"/>
-      <c r="C38" s="108"/>
-      <c r="L38" s="87"/>
-      <c r="W38" s="87"/>
+      <c r="A38" s="110"/>
+      <c r="B38" s="110"/>
+      <c r="C38" s="111"/>
+      <c r="L38" s="86"/>
+      <c r="W38" s="86"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A39" s="107" t="s">
+      <c r="A39" s="110" t="s">
         <v>163</v>
       </c>
-      <c r="B39" s="107"/>
-      <c r="C39" s="108"/>
-      <c r="L39" s="87"/>
-      <c r="W39" s="87"/>
+      <c r="B39" s="110"/>
+      <c r="C39" s="111"/>
+      <c r="L39" s="86"/>
+      <c r="W39" s="86"/>
     </row>
     <row r="40" spans="1:23" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="107"/>
-      <c r="B40" s="107"/>
-      <c r="C40" s="108"/>
-      <c r="L40" s="87"/>
-      <c r="W40" s="87"/>
+      <c r="A40" s="110"/>
+      <c r="B40" s="110"/>
+      <c r="C40" s="111"/>
+      <c r="L40" s="86"/>
+      <c r="W40" s="86"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A41" s="107" t="s">
+      <c r="A41" s="110" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="107"/>
-      <c r="C41" s="108"/>
-      <c r="L41" s="87"/>
-      <c r="W41" s="87"/>
+      <c r="B41" s="110"/>
+      <c r="C41" s="111"/>
+      <c r="L41" s="86"/>
+      <c r="W41" s="86"/>
     </row>
     <row r="42" spans="1:23" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="107"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="108"/>
-      <c r="L42" s="87"/>
-      <c r="W42" s="87"/>
+      <c r="A42" s="110"/>
+      <c r="B42" s="110"/>
+      <c r="C42" s="111"/>
+      <c r="L42" s="86"/>
+      <c r="W42" s="86"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A43" s="107" t="s">
+      <c r="A43" s="110" t="s">
         <v>165</v>
       </c>
-      <c r="B43" s="107"/>
-      <c r="C43" s="108"/>
-      <c r="L43" s="87"/>
-      <c r="W43" s="87"/>
+      <c r="B43" s="110"/>
+      <c r="C43" s="111"/>
+      <c r="L43" s="86"/>
+      <c r="W43" s="86"/>
     </row>
     <row r="44" spans="1:23" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="107"/>
-      <c r="B44" s="107"/>
-      <c r="C44" s="108"/>
-      <c r="L44" s="87"/>
-      <c r="W44" s="87"/>
+      <c r="A44" s="110"/>
+      <c r="B44" s="110"/>
+      <c r="C44" s="111"/>
+      <c r="L44" s="86"/>
+      <c r="W44" s="86"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" s="107" t="s">
+      <c r="A45" s="110" t="s">
         <v>166</v>
       </c>
-      <c r="B45" s="107"/>
-      <c r="C45" s="108"/>
-      <c r="L45" s="87"/>
-      <c r="W45" s="87"/>
+      <c r="B45" s="110"/>
+      <c r="C45" s="111"/>
+      <c r="L45" s="86"/>
+      <c r="W45" s="86"/>
     </row>
     <row r="46" spans="1:23" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="107"/>
-      <c r="B46" s="107"/>
-      <c r="C46" s="108"/>
-      <c r="L46" s="87"/>
-      <c r="W46" s="87"/>
+      <c r="A46" s="110"/>
+      <c r="B46" s="110"/>
+      <c r="C46" s="111"/>
+      <c r="L46" s="86"/>
+      <c r="W46" s="86"/>
     </row>
     <row r="47" spans="1:23" ht="6.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="87"/>
-      <c r="L47" s="87"/>
-      <c r="W47" s="87"/>
+      <c r="A47" s="103"/>
+      <c r="C47" s="86"/>
+      <c r="L47" s="86"/>
+      <c r="W47" s="86"/>
     </row>
     <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="84"/>
-      <c r="C48" s="87"/>
-      <c r="L48" s="87"/>
-      <c r="W48" s="87"/>
+      <c r="A48" s="103"/>
+      <c r="C48" s="86"/>
+      <c r="L48" s="86"/>
+      <c r="W48" s="86"/>
     </row>
     <row r="49" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="93"/>
-      <c r="B49" s="85"/>
-      <c r="C49" s="88"/>
-      <c r="D49" s="85"/>
-      <c r="E49" s="85"/>
-      <c r="F49" s="85"/>
-      <c r="G49" s="85"/>
-      <c r="H49" s="85"/>
-      <c r="I49" s="85"/>
-      <c r="J49" s="85"/>
-      <c r="K49" s="85"/>
-      <c r="L49" s="88"/>
-      <c r="M49" s="85"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="85"/>
-      <c r="P49" s="85"/>
-      <c r="Q49" s="85"/>
-      <c r="R49" s="85"/>
-      <c r="S49" s="85"/>
-      <c r="T49" s="85"/>
-      <c r="U49" s="85"/>
-      <c r="V49" s="85"/>
-      <c r="W49" s="88"/>
+      <c r="A49" s="88"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="87"/>
+      <c r="D49" s="84"/>
+      <c r="E49" s="84"/>
+      <c r="F49" s="84"/>
+      <c r="G49" s="84"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="84"/>
+      <c r="J49" s="84"/>
+      <c r="K49" s="84"/>
+      <c r="L49" s="87"/>
+      <c r="M49" s="84"/>
+      <c r="N49" s="84"/>
+      <c r="O49" s="84"/>
+      <c r="P49" s="84"/>
+      <c r="Q49" s="84"/>
+      <c r="R49" s="84"/>
+      <c r="S49" s="84"/>
+      <c r="T49" s="84"/>
+      <c r="U49" s="84"/>
+      <c r="V49" s="84"/>
+      <c r="W49" s="87"/>
     </row>
     <row r="50" spans="1:23" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -26386,21 +26193,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="92"/>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="109" t="s">
+      <c r="A1" s="89"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="112" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
       <c r="N1" s="18"/>
       <c r="O1" s="18"/>
       <c r="P1" s="18"/>
@@ -26432,7 +26239,7 @@
       <c r="L2" t="s">
         <v>152</v>
       </c>
-      <c r="M2" s="94" t="s">
+      <c r="M2" s="90" t="s">
         <v>160</v>
       </c>
       <c r="N2" s="8"/>
@@ -26472,9 +26279,9 @@
         <f t="shared" ref="L3:L29" si="0">IF(RANK(I3, $I$3:$I$29,0)&lt;=10, "YES", "NO")</f>
         <v>NO</v>
       </c>
-      <c r="M3" s="95">
+      <c r="M3" s="91">
         <f t="shared" ref="M3:M29" ca="1" si="1">NOW()</f>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N3" s="8"/>
       <c r="O3" s="8"/>
@@ -26513,9 +26320,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M4" s="98">
+      <c r="M4" s="94">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
@@ -26554,9 +26361,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M5" s="95">
+      <c r="M5" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -26595,9 +26402,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M6" s="95">
+      <c r="M6" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
@@ -26636,9 +26443,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M7" s="95">
+      <c r="M7" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -26677,9 +26484,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M8" s="98">
+      <c r="M8" s="94">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
@@ -26718,9 +26525,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -26759,9 +26566,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M10" s="98">
+      <c r="M10" s="94">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
@@ -26800,9 +26607,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M11" s="95">
+      <c r="M11" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
@@ -26841,9 +26648,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M12" s="95">
+      <c r="M12" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="16"/>
@@ -26882,9 +26689,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M13" s="98">
+      <c r="M13" s="94">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N13" s="16"/>
       <c r="O13" s="16"/>
@@ -26923,9 +26730,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M14" s="95">
+      <c r="M14" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
@@ -26964,9 +26771,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M15" s="95">
+      <c r="M15" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
@@ -27005,9 +26812,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M16" s="95">
+      <c r="M16" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
@@ -27046,9 +26853,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M17" s="95">
+      <c r="M17" s="91">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
@@ -27087,9 +26894,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M18" s="96">
+      <c r="M18" s="92">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
@@ -27128,9 +26935,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M19" s="97">
+      <c r="M19" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -27164,9 +26971,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M20" s="99">
+      <c r="M20" s="95">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -27200,9 +27007,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M21" s="99">
+      <c r="M21" s="95">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -27236,9 +27043,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M22" s="99">
+      <c r="M22" s="95">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -27272,9 +27079,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M23" s="99">
+      <c r="M23" s="95">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -27308,9 +27115,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M24" s="97">
+      <c r="M24" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.3">
@@ -27344,9 +27151,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M25" s="97">
+      <c r="M25" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.3">
@@ -27380,9 +27187,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M26" s="99">
+      <c r="M26" s="95">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
@@ -27416,9 +27223,9 @@
         <f t="shared" si="0"/>
         <v>YES</v>
       </c>
-      <c r="M27" s="99">
+      <c r="M27" s="95">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.3">
@@ -27452,9 +27259,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M28" s="97">
+      <c r="M28" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.3">
@@ -27488,9 +27295,9 @@
         <f t="shared" si="0"/>
         <v>NO</v>
       </c>
-      <c r="M29" s="97">
+      <c r="M29" s="93">
         <f t="shared" ca="1" si="1"/>
-        <v>46276.457523611112</v>
+        <v>46280.596419791669</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.3">
@@ -27550,22 +27357,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="113" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A3" s="111" t="s">
+      <c r="A3" s="114" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="111"/>
+      <c r="B3" s="114"/>
       <c r="D3" s="74" t="s">
         <v>148</v>
       </c>
@@ -27653,10 +27460,10 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="A8" s="111" t="s">
+      <c r="A8" s="114" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="111"/>
+      <c r="B8" s="114"/>
       <c r="D8" s="58">
         <v>0.2</v>
       </c>
@@ -27763,28 +27570,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.3">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="113" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="K1" s="114" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="K1" s="117" t="s">
         <v>156</v>
       </c>
-      <c r="L1" s="115"/>
-      <c r="M1" s="116"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="119"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="115" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="113"/>
+      <c r="B2" s="116"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
@@ -28272,21 +28079,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="120" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="119"/>
-      <c r="E1" s="120" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="122"/>
+      <c r="E1" s="123" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="75" t="s">
@@ -28690,25 +28497,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="120" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="119"/>
-      <c r="I1" s="121" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="122"/>
+      <c r="I1" s="124" t="s">
         <v>151</v>
       </c>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="123"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="125"/>
+      <c r="L1" s="125"/>
+      <c r="M1" s="125"/>
+      <c r="N1" s="125"/>
+      <c r="O1" s="125"/>
+      <c r="P1" s="126"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
@@ -28885,58 +28692,58 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="100" t="s">
+      <c r="A12" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="B12" s="100" t="s">
+      <c r="B12" s="96" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="101" t="s">
+      <c r="A13" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="102">
+      <c r="B13" s="98">
         <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="102">
+      <c r="B14" s="98">
         <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="101" t="s">
+      <c r="A15" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="102">
+      <c r="B15" s="98">
         <v>383</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="101" t="s">
+      <c r="A16" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="102">
+      <c r="B16" s="98">
         <v>374</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="101" t="s">
+      <c r="A17" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="102">
+      <c r="B17" s="98">
         <v>458</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="99" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="104">
+      <c r="B18" s="100">
         <v>1999</v>
       </c>
     </row>
